--- a/outputs/Block5B_Senate_Attribution_Summary.xlsx
+++ b/outputs/Block5B_Senate_Attribution_Summary.xlsx
@@ -34,16 +34,16 @@
     <t>National bucket prior R after</t>
   </si>
   <si>
-    <t>Canonical Democratic Senate After</t>
-  </si>
-  <si>
-    <t>Canonical Republican Senate After</t>
-  </si>
-  <si>
-    <t>Canonical Democratic-held seats lost</t>
-  </si>
-  <si>
-    <t>Canonical Republican-held seats lost</t>
+    <t>Provisional marginal-favorite Democratic Senate After</t>
+  </si>
+  <si>
+    <t>Provisional marginal-favorite Republican Senate After</t>
+  </si>
+  <si>
+    <t>Provisional Democratic-held seats lost</t>
+  </si>
+  <si>
+    <t>Provisional Republican-held seats lost</t>
   </si>
   <si>
     <t>Modeled Senate races</t>
@@ -511,7 +511,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -519,7 +519,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -527,7 +527,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -535,7 +535,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -543,7 +543,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -551,7 +551,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -591,7 +591,7 @@
         <v>14</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -607,7 +607,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>4.9282</v>
+        <v>7.2686</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -615,7 +615,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>0.9246</v>
+        <v>0.3417</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -623,7 +623,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>2.5338</v>
+        <v>2.9021</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -631,7 +631,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>1.6092</v>
+        <v>2.5603</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -639,7 +639,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>3.4584</v>
+        <v>3.2438</v>
       </c>
     </row>
     <row r="21" spans="1:2">
